--- a/outputs/tables/visual_items_llm_summary.xlsx
+++ b/outputs/tables/visual_items_llm_summary.xlsx
@@ -431,7 +431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>item_raw</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -492,28 +492,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -546,10 +546,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="4">
@@ -564,16 +564,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -600,16 +600,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -636,22 +636,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -672,22 +672,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -708,22 +708,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -744,22 +744,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -780,28 +780,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/visual_items_llm_summary.xlsx
+++ b/outputs/tables/visual_items_llm_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
